--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Map101</t>
-  </si>
-  <si>
-    <t>#封测二区</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1160,7 +1157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O381"/>
+  <dimension ref="A3:O376"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="7" customWidth="1"/>
@@ -1367,116 +1364,18 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="13">
-        <v>201</v>
-      </c>
-      <c r="D13" s="10">
-        <v>2</v>
-      </c>
-      <c r="E13" s="10">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="8">
-        <v>20335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="13">
-        <v>202</v>
-      </c>
-      <c r="D14" s="10">
-        <v>2</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="10">
-        <v>20336</v>
-      </c>
-    </row>
-    <row r="15" s="7" customFormat="1" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="13">
-        <v>203</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="8">
-        <v>20337</v>
-      </c>
-    </row>
-    <row r="16" s="7" customFormat="1" spans="3:8">
-      <c r="C16" s="13">
-        <v>204</v>
-      </c>
-      <c r="D16" s="10">
-        <v>2</v>
-      </c>
-      <c r="E16" s="10">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" s="7" customFormat="1" spans="3:8">
-      <c r="C17" s="13">
-        <v>213</v>
-      </c>
-      <c r="D17" s="10">
-        <v>2</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" s="7" customFormat="1" spans="3:7">
-      <c r="C18" s="13"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-    </row>
+    <row r="13" s="7" customFormat="1" spans="3:7">
+      <c r="C13" s="13"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" s="7" customFormat="1"/>
+    <row r="15" s="7" customFormat="1"/>
+    <row r="16" s="7" customFormat="1"/>
+    <row r="17" s="7" customFormat="1"/>
+    <row r="18" s="7" customFormat="1"/>
     <row r="19" s="7" customFormat="1"/>
     <row r="20" s="7" customFormat="1"/>
     <row r="21" s="7" customFormat="1"/>
@@ -1833,26 +1732,21 @@
     <row r="372" s="7" customFormat="1"/>
     <row r="373" s="7" customFormat="1"/>
     <row r="374" s="7" customFormat="1"/>
-    <row r="375" s="7" customFormat="1"/>
-    <row r="376" s="7" customFormat="1"/>
-    <row r="377" s="7" customFormat="1"/>
-    <row r="378" s="7" customFormat="1"/>
-    <row r="379" s="7" customFormat="1"/>
-    <row r="380" s="7" customFormat="1" spans="3:8">
-      <c r="C380" s="11"/>
-      <c r="D380" s="8"/>
-      <c r="E380" s="8"/>
-      <c r="F380" s="8"/>
-      <c r="G380" s="8"/>
-      <c r="H380" s="8"/>
-    </row>
-    <row r="381" s="7" customFormat="1" spans="3:8">
-      <c r="C381" s="11"/>
-      <c r="D381" s="8"/>
-      <c r="E381" s="8"/>
-      <c r="F381" s="8"/>
-      <c r="G381" s="8"/>
-      <c r="H381" s="8"/>
+    <row r="375" s="7" customFormat="1" spans="3:8">
+      <c r="C375" s="11"/>
+      <c r="D375" s="8"/>
+      <c r="E375" s="8"/>
+      <c r="F375" s="8"/>
+      <c r="G375" s="8"/>
+      <c r="H375" s="8"/>
+    </row>
+    <row r="376" s="7" customFormat="1" spans="3:8">
+      <c r="C376" s="11"/>
+      <c r="D376" s="8"/>
+      <c r="E376" s="8"/>
+      <c r="F376" s="8"/>
+      <c r="G376" s="8"/>
+      <c r="H376" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1969,10 +1863,10 @@
         <v>1000</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="10">
         <v>30310</v>
@@ -1989,10 +1883,10 @@
         <v>1000</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="10">
         <v>30311</v>
@@ -2009,10 +1903,10 @@
         <v>1000</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="10"/>
     </row>
@@ -2132,10 +2026,10 @@
         <v>1001</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -2294,10 +2188,10 @@
         <v>1002</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5">
         <v>30300</v>
@@ -2316,10 +2210,10 @@
         <v>1002</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="H7" s="5">
         <v>30301</v>
@@ -2338,10 +2232,10 @@
         <v>1002</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="5">
         <v>30302</v>
@@ -2360,10 +2254,10 @@
         <v>1002</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="5">
         <v>30303</v>
@@ -2382,10 +2276,10 @@
         <v>1002</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="5">
         <v>30304</v>
